--- a/resultados/Swift_manuales.xlsx
+++ b/resultados/Swift_manuales.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,30 +482,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5c21184b-beb9-5cc1-b4f0-3cc9acad81ef</t>
+          <t>355073dc-58f7-51e7-826e-403a8a6a3b2b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11927 TUSA DIS TICARET.pdf</t>
+          <t>13286 14518 SOORTY ENTERPRISES.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CHASUS33XXX</t>
+          <t>BKTRUS33XXX</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TUSA DIS TICARET AS</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>ESTADOS UNIDOS</t>
@@ -518,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TUSA DIS TICARET AS CHASUS33XXX</t>
+          <t>BKTRUS33XXX</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -532,30 +528,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ad1bf8f9-7171-590d-851c-34ace869526e</t>
+          <t>83a25f24-8afb-5b58-9597-9e7beb079b9d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13120 13121 SHANGHAI DAYA.pdf</t>
+          <t>13310 TEXTIL CANATIBA.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOFAUS3MXXX</t>
+          <t>BKTRUS33XXX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SHANGHAI DAYA IMPORT AND EXPORT CO LTD</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>ESTADOS UNIDOS</t>
@@ -563,12 +555,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>NUEVA YORK</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SHANGHAI DAYA IMPORT AND EXPORT CO LTD BOFAUS3MXXX</t>
+          <t>BKTRUS33XXX</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -578,6 +570,4232 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bf2d9caa-3493-5146-a36e-40c2ab4e2479</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13357 FOSHAN BLUE.pdf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8e5fe3a2-6705-53d9-aea5-d30de2f188ed</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13379 14687 ARTISTIC MILLINERS.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6d11bfda-70a3-5526-abf5-44f2653f0d84</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13401 13707 WUJIANG LA MODE.pdf</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>73bbaf19-03b8-5aa5-bcdc-83225505be2f</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13414 SHAOXING TUJIA.pdf</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>82802a2d-c104-5641-8854-90a1bb79a678</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13430 SEDATEX.pdf</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>66d854b9-7d8c-5e38-a55e-aa291b67c964</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13460 KIPAS PAZARLAME.pdf</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2d333b26-d46d-505d-8217-87fa7c71e454</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13464 SHAOXING QIFEI.pdf</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>b8a8bd51-2530-57dd-b55e-b2265e369278</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13467 DEPEI.pdf</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>d45c6a0d-c097-5e5b-aa8c-8bd90ba54101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13506 RAYMOND UCO DENIM.pdf</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6343d381-a8c5-599a-a809-1484a25105c0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13524 TEXTIL CANATIBA.pdf</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>d626d663-6395-5889-978e-6417bdf43ea9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13560 SANKO.pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CAIXESBBXXX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BARCELONA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CAIXESBBXXX</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fcb8062d-2978-58f3-a8f8-d10c8ff7309c</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13573 PROSPERITY TEXTILE.pdf</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>a8dd012c-367f-535c-a0c8-9c4c7ae97f1d</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13599 13912 14546 FOSHAN BLUE.pdf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1101bccb-00e2-5ca0-a71c-41a416a9eca8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13610 HEBEI XINDADONG.pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>d75deac0-13d2-5207-b5d8-00c6f7ff93cd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13629 13628 14532 ARTISTIC MILLINERS.pdf</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>902d37ed-ed0c-5541-9b17-5046f3c8bf95</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13632 13489 13632 SHAOXING ADA.pdf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7e3684b2-f74c-5739-8ea6-fba23c109a8c</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13665 13479 JIANGSU PINYTEX.pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5063bdc6-9a16-584d-89a8-9d81fb1f94b5</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13675 TEXTIL CANATIBA.pdf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>994884cf-3504-5980-b706-80cf66514c45</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13784 14406 FOSHAN BLUE.pdf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>d47e1913-d38c-5040-916f-72d77379d16e</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13786 YULIN YIXING SPINNING.pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8827058a-f503-588b-8958-d6436c326fd0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13791 13792 SOORTY ENTERPRISES 2.pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4f9a72ba-4457-57ac-8880-07a6f144f484</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13791 13792 SOORTY ENTERPRISES.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2be8a378-25bb-5254-b574-eda0a3d47f30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13795 KIPAS PAZARLAME.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>b9ca8ecb-02b9-5d77-8f23-3159d20dc047</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13813 13812 CREDITEX.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3f269209-b70f-5b11-9375-808671854841</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13818 14229 FOSHAN BLUE.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1452.00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>24492ba1-b2a0-5628-a40d-101c0b9e1e76</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>13828 ZHEJIANG LESON.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>af14b70e-6c63-5e38-81af-d244d4eab4b9</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>13856 13464 SHAOXING QIFEI.pdf</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CITIUS33XXX</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CITIUS33XXX</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cb82c529-4c63-5908-956c-1020101e8085</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>13857 SHAOXING QIFEI.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>baa54e73-4f23-514a-b378-2c107096ed2d</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13862 13851 SHANGHAI DAYA.pdf</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3a549f60-7043-5eb0-907e-8f214d0dd76e</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>13875 SHAOXING TUJIA.pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2ecb397e-5956-5a1b-bd75-4724ce37273a</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>13879 14137 WUJIANG LA MODE.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>43e81fb6-098d-5624-b879-e71819b93df4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>13910 14627 DEPEI.pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>32354051-b082-5185-8b08-fc1add988174</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>13911 14553 FOSHAN BLUE.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5801737f-e98c-550e-a336-a9e76f4d2ecf</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>13915 14346 14170 SHAOXING QIFEI.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>da316acc-99a4-567a-bf35-bae14ab3202a</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>13920 SHAOXING NAYING.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>b2163094-837b-5443-aed7-4a7fa0c9b8d6</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>13955 13847 SEDATEX.pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>d427e1b8-3af3-5f29-9052-4f74d6acd0db</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>13960 SEDATEX.pdf</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2212ce4c-8041-517b-8768-ccd587584479</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>13978 SHAOXING TUJIA.pdf</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>d9895abe-5bb9-58b9-b7f0-a9422560a08d</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>13980 GESI TEKSTIL.pdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>5ca4664a-4002-5b60-bab1-03ae73d08b25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>13985 SANTISTA TEXTIL.pdf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>02181447</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>02181447</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9ec0f9aa-7098-5017-a120-35fd5c18f9bb</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>13986 ZHEJIANG LESOSN.pdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>e379f6a9-8ca6-55bd-bf56-fc02491f7e27</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>13991 ORTA ANADOLU.pdf</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>520afb13-0575-568f-82ce-3ef677205869</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>14049 AKBASLAR TEKSTIL.pdf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bcf9bced-4f9b-5320-8f5a-7bbb50590537</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>14050 14439 AKBASLAR TEKSTIL.pdf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>f74b90fa-dad6-5c50-bd35-18f3282a33fa</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>14057 GESI TEKSTIL.pdf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>02041508</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>02041508</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>60a8734d-d8f9-5b83-9684-01c97c1a35a8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>14060 SHAOXING JINZHOU.pdf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cc8f8501-5133-5c9d-bd01-4b59d0871e57</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>14081 SEDATEX.pdf</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>42495d9c-58c0-5024-bb3d-d4f5e8a0a61d</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>14095 DEPEI.pdf</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>d030c2c4-8942-5a21-8b61-22f50c22826f</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>14103 CATAGUASES.pdf</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3d978b49-98d4-5fae-810c-362dad79c187</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>14109 SOORTY ENTERPRISES.pdf</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>628927c6-cb6e-53dc-85a9-e7d93b553719</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>14123 HEBEI XINDADONG.pdf</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>b6ef95b6-d99c-547a-8ccf-cb5de16e0898</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>14131 14129 14629 AKBASLAR.pdf</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0193ad80-ae61-5e11-81b2-56f5a00229a7</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>14132 AKBASLAR TEKSTIL.pdf</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>b0c7d3ab-9a8e-573e-8b6b-04624dbf7b1f</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>14134 CHRIS J CORPORATION.pdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>b837a516-2cb1-59c6-a61c-601b4ab8f108</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>14135 14660 14661 WUJIANG LA MODE.pdf</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20186d17-0866-59fc-80b2-c229f6f369db</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>14140 BMS FASHION.pdf</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fb481d58-f79a-5f10-9595-93bbe61500ca</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>14164 NAVEENA.pdf</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>df2b6b4d-0d04-5a6a-a901-93f48df0120a</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>14174 ARTISTIC MILLINERS.pdf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1321b9fb-6e90-530c-9e6a-ac4dc1f75ae1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>14180 ZHEJIANG LESON.pdf</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>5035811a-5602-5dc7-979e-dfd4e0f32b67</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>14193 HEBEI XINDADONG.pdf</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>75e3b676-d09b-5031-910c-b67754c49c64</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>14197 HEBEI XINDADONG.pdf</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>8e319aa3-cf38-5800-8eb8-3f7196b490b1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>14232 13581 YULIN YIXING.pdf</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1c97c4aa-5e9e-5799-9c5a-5fb853a8de5b</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>14248 14322 JIANGSU PINYTEX.pdf</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>033db291-6459-5213-8f26-41083a9d3f12</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>14257 14274 NANTONG JIAHENG.pdf</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>9f97b048-6de3-59df-8eab-73b98c8dd520</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>14259 NANTONG JIAHENG.pdf</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>221772ef-10c2-5a2c-bf6b-52aabcf01cb3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>14285 14287 SHAFI TEXCEL.pdf</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>507df882-3b24-5c43-85bf-e9deff9b1d07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>14341 GID LLC.pdf</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>13ad17cc-6e74-571e-b24a-be88f1059880</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>14344 NANTONG JIAHENG.pdf</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>d8cb7863-6be5-5806-b2a8-ec088ffb8ee1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>14352 14355 14139 GID LLC.pdf</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2a35b18f-afef-51ec-8ffd-bbc090a4fb7a</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>14354 YULIN YIXING.pdf</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>34a382a9-eb13-5e3b-ad3a-4ab01b0905fc</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>14356 14357 14537 YULIN YUXING.pdf</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>bcaa30c6-bc59-5a48-ba54-e1b06669d83a</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>14376 ARTISTIC FABRICS MILLS.pdf</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>6921bd28-7bdd-53fd-8d37-ef572126281c</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>14377 14378 ARTISTIC FABRIC MILLS.pdf</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>e7686b47-be02-5781-8ff5-c5600c9f0a4a</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>14415 14416 14480 14481 ZHEJIANG LESON IMP EXP.pdf</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>c91d97c1-f664-50e9-970c-f236969b1826</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>14455 FOSHAN BLUE.pdf</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>02181447</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>02181447</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>154fc199-416f-5fd1-895b-31443813eda2</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>14469 14566 GID LLC.pdf</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3abb1465-b52f-503e-96f0-27614153b83a</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>14499 SANKO.pdf</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>365c56a3-9abc-51ac-91f2-fc03d8adaf7a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>14519 ARTISTIC FABRICS.pdf</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>a5ae968b-22ae-51a1-b087-e2f541619672</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>14528 NANTONG JIAHENG.pdf</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ceea824b-8dc4-5a4c-aeb2-39bec4de3792</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>14533 14534 XIN XING LONG.pdf</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>6ac61a6a-0e3d-529d-b2e8-7e166df5e67f</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>14534 XIN XING LONG.pdf</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3273326a-c637-5d2e-bc6c-ea1dd9fd4d1c</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>14565 14667 GID LLC.pdf</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>695c9d1d-c130-54ef-863a-690f7342ef31</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>14586 14587 ARTISTIC FABRIC MILLS.pdf</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>493f542c-ecf0-5866-99e1-92dd3f8cb9be</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>14588 14589 CHRIS J.pdf</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>777df970-1a5c-5056-837a-21689baa523b</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>14591 CREDITEX.pdf</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>9beb05c1-edc5-58c0-b664-1cd698d947c4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>14595 14596 14598 14599 HANGZHOU SANJIN.pdf</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>13110565-a7c6-5255-a3d6-62d0796261d0</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>14600 14601 WUJIANG LA MODE.pdf</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cbc356dd-29d9-5141-88c3-90caabe95232</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>14602 ORTA ANADOLU.pdf</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>e1080833-4651-51f1-9a69-505c53e5275a</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>14628 ARTISTIC FABRIC MILLS.pdf</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ee39da1c-9ee8-532c-bf61-3d36a114e1ae</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>14643 MALHAS MENEGOTTI.pdf</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>235a8f09-49c6-5f41-b703-08217820d4ae</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>14657 14658 SHAOXING NAYING.pdf</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>a9dda61a-4177-594e-bcf5-2700383e87c1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>14668 14669 SHAOXING SAGA.pdf</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>COLOPAPAXXX</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1022c774-82ce-550d-ad54-306d9970af69</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>14714 14715 WUJIANG LA MODE.pdf</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>IRVTUS3NXXX</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
